--- a/research/traditional_assets/database/data/argentina/argentina_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,47 +587,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.412</v>
-      </c>
-      <c r="E2">
-        <v>-0.38</v>
-      </c>
       <c r="G2">
-        <v>0.3410822206605763</v>
+        <v>0.4794635193133048</v>
       </c>
       <c r="H2">
-        <v>0.3387210119465917</v>
+        <v>0.4753218884120172</v>
       </c>
       <c r="I2">
-        <v>0.2565003513703443</v>
+        <v>0.3583690987124464</v>
       </c>
       <c r="J2">
-        <v>0.2070452836236762</v>
+        <v>0.2687768240343348</v>
       </c>
       <c r="K2">
-        <v>-18.812</v>
+        <v>5.34</v>
       </c>
       <c r="L2">
-        <v>-0.1321995783555868</v>
+        <v>0.0572961373390558</v>
       </c>
       <c r="M2">
-        <v>17.891</v>
+        <v>19.28</v>
       </c>
       <c r="N2">
-        <v>0.01432770080884119</v>
+        <v>0.0150390015600624</v>
       </c>
       <c r="O2">
-        <v>-0.9510418881564957</v>
+        <v>3.610486891385768</v>
       </c>
       <c r="P2">
-        <v>17.891</v>
+        <v>19.28</v>
       </c>
       <c r="Q2">
-        <v>0.01432770080884119</v>
+        <v>0.0150390015600624</v>
       </c>
       <c r="R2">
-        <v>-0.9510418881564957</v>
+        <v>3.610486891385768</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>679.2</v>
+        <v>593.5999999999999</v>
       </c>
       <c r="V2">
-        <v>0.5439256827100184</v>
+        <v>0.4630265210608424</v>
       </c>
       <c r="W2">
-        <v>0.01403409090909091</v>
+        <v>0.0317270203152383</v>
       </c>
       <c r="X2">
-        <v>0.04621177438595881</v>
+        <v>0.08103441937928031</v>
       </c>
       <c r="Y2">
-        <v>-0.0321776834768679</v>
-      </c>
-      <c r="Z2">
-        <v>-0.3857518501450297</v>
-      </c>
-      <c r="AA2">
-        <v>-0.0935937433223642</v>
+        <v>-0.04930739906404201</v>
       </c>
       <c r="AB2">
-        <v>0.04625573277293367</v>
-      </c>
-      <c r="AC2">
-        <v>-0.1397865674016494</v>
+        <v>0.08137254261537472</v>
       </c>
       <c r="AD2">
-        <v>7.756</v>
+        <v>5.28</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7.756</v>
+        <v>5.28</v>
       </c>
       <c r="AG2">
-        <v>-671.4440000000001</v>
+        <v>-588.3199999999999</v>
       </c>
       <c r="AH2">
-        <v>0.006172918112532393</v>
+        <v>0.00410167174196756</v>
       </c>
       <c r="AI2">
-        <v>0.01505271166177589</v>
+        <v>0.01072560331518648</v>
       </c>
       <c r="AJ2">
-        <v>-1.163165042892582</v>
+        <v>-0.8481144043362933</v>
       </c>
       <c r="AK2">
-        <v>4.095569218757623</v>
+        <v>5.806553493880777</v>
       </c>
       <c r="AL2">
-        <v>0.017</v>
+        <v>0.354</v>
       </c>
       <c r="AM2">
-        <v>-3.543</v>
+        <v>-4.405</v>
       </c>
       <c r="AN2">
-        <v>0.191980198019802</v>
+        <v>0.1423180592991914</v>
       </c>
       <c r="AO2">
-        <v>2147.058823529412</v>
+        <v>94.35028248587572</v>
       </c>
       <c r="AP2">
-        <v>-16.61990099009901</v>
+        <v>-15.85768194070081</v>
       </c>
       <c r="AQ2">
-        <v>-10.30200395145357</v>
+        <v>-7.582292849035188</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Financiero Valores S.A. (BASE:GFVA)</t>
+          <t>Matba Rofex S.A. (BASE:MTR)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,47 +706,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.412</v>
-      </c>
-      <c r="E3">
-        <v>-0.38</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.4953186274509804</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.4950980392156863</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.4240196078431373</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.4240196078431373</v>
       </c>
       <c r="K3">
-        <v>0.988</v>
+        <v>8.23</v>
       </c>
       <c r="L3">
-        <v>0.01563291139240506</v>
+        <v>0.2017156862745098</v>
       </c>
       <c r="M3">
-        <v>5.031</v>
+        <v>6.38</v>
       </c>
       <c r="N3">
-        <v>0.02327012025901943</v>
+        <v>0.01846064814814815</v>
       </c>
       <c r="O3">
-        <v>5.092105263157895</v>
+        <v>0.7752126366950182</v>
       </c>
       <c r="P3">
-        <v>5.031</v>
+        <v>6.38</v>
       </c>
       <c r="Q3">
-        <v>0.02327012025901943</v>
+        <v>0.01846064814814815</v>
       </c>
       <c r="R3">
-        <v>5.092105263157895</v>
+        <v>0.7752126366950182</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,61 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>102.8</v>
+        <v>270.7</v>
       </c>
       <c r="V3">
-        <v>0.4754856614246069</v>
+        <v>0.7832754629629629</v>
       </c>
       <c r="W3">
-        <v>0.01403409090909091</v>
+        <v>0.07309058614564833</v>
       </c>
       <c r="X3">
-        <v>0.04700590908626032</v>
+        <v>0.08124308890114179</v>
       </c>
       <c r="Y3">
-        <v>-0.03297181817716942</v>
-      </c>
-      <c r="Z3">
-        <v>-0.6351758793969849</v>
-      </c>
-      <c r="AA3">
-        <v>-0</v>
+        <v>-0.008152502755493465</v>
       </c>
       <c r="AB3">
-        <v>0.04870898050163067</v>
-      </c>
-      <c r="AC3">
-        <v>-0.04870898050163067</v>
+        <v>0.08191933537333058</v>
       </c>
       <c r="AD3">
-        <v>7.54</v>
+        <v>5.28</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.54</v>
+        <v>5.28</v>
       </c>
       <c r="AG3">
-        <v>-95.25999999999999</v>
+        <v>-265.42</v>
       </c>
       <c r="AH3">
-        <v>0.03369983016000715</v>
+        <v>0.01504787961696307</v>
       </c>
       <c r="AI3">
-        <v>0.07574844283705043</v>
+        <v>0.03551251008878128</v>
       </c>
       <c r="AJ3">
-        <v>-0.7876633041177443</v>
+        <v>-3.310301820902968</v>
       </c>
       <c r="AK3">
-        <v>29.2208588957056</v>
+        <v>2.175217177511883</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.006000000000000005</v>
+      </c>
+      <c r="AN3">
+        <v>0.2764397905759162</v>
+      </c>
+      <c r="AO3">
+        <v>182.1052631578947</v>
+      </c>
+      <c r="AP3">
+        <v>-13.89633507853403</v>
+      </c>
+      <c r="AQ3">
+        <v>2883.333333333331</v>
       </c>
     </row>
     <row r="4">
@@ -844,40 +826,40 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.7076363636363636</v>
+        <v>0.467118320610687</v>
       </c>
       <c r="H4">
-        <v>0.7000000000000001</v>
+        <v>0.4599236641221374</v>
       </c>
       <c r="I4">
-        <v>0.4977272727272727</v>
+        <v>0.3072519083969466</v>
       </c>
       <c r="J4">
-        <v>0.4977272727272727</v>
+        <v>0.1536259541984733</v>
       </c>
       <c r="K4">
-        <v>-30</v>
+        <v>-2.89</v>
       </c>
       <c r="L4">
-        <v>-0.6818181818181818</v>
+        <v>-0.0551526717557252</v>
       </c>
       <c r="M4">
-        <v>5.25</v>
+        <v>12.9</v>
       </c>
       <c r="N4">
-        <v>0.006803161850460023</v>
+        <v>0.01377616403246476</v>
       </c>
       <c r="O4">
-        <v>-0.175</v>
+        <v>-4.463667820069204</v>
       </c>
       <c r="P4">
-        <v>5.25</v>
+        <v>12.9</v>
       </c>
       <c r="Q4">
-        <v>0.006803161850460023</v>
+        <v>0.01377616403246476</v>
       </c>
       <c r="R4">
-        <v>-0.175</v>
+        <v>-4.463667820069204</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -886,198 +868,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>468.2</v>
+        <v>322.9</v>
       </c>
       <c r="V4">
-        <v>0.6067124530257871</v>
+        <v>0.3448312686885946</v>
       </c>
       <c r="W4">
-        <v>-0.1083423618634886</v>
+        <v>-0.009636545515171725</v>
       </c>
       <c r="X4">
-        <v>0.0461926999735028</v>
+        <v>0.08082574985741883</v>
       </c>
       <c r="Y4">
-        <v>-0.1545350618369914</v>
-      </c>
-      <c r="Z4">
-        <v>-0.1880422240266678</v>
-      </c>
-      <c r="AA4">
-        <v>-0.0935937433223642</v>
+        <v>-0.09046229537259055</v>
       </c>
       <c r="AB4">
-        <v>0.04619282407928521</v>
-      </c>
-      <c r="AC4">
-        <v>-0.1397865674016494</v>
+        <v>0.08082574985741883</v>
       </c>
       <c r="AD4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>-468.198</v>
+        <v>-322.9</v>
       </c>
       <c r="AH4">
-        <v>2.591673988145683e-06</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>6.668845156084322e-06</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-1.542652107729108</v>
+        <v>-0.5263243683781581</v>
       </c>
       <c r="AK4">
-        <v>2.78195819320491</v>
+        <v>-15.59903381642509</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.259</v>
       </c>
       <c r="AM4">
-        <v>-3.56</v>
+        <v>-4.411</v>
       </c>
       <c r="AN4">
-        <v>8.230452674897119e-05</v>
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>62.16216216216217</v>
       </c>
       <c r="AP4">
-        <v>-19.2674074074074</v>
+        <v>-17.93888888888889</v>
       </c>
       <c r="AQ4">
-        <v>-6.151685393258426</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Argentina</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Matba Rofex S.A. (BASE:MTR)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="G5">
-        <v>0.4957264957264957</v>
-      </c>
-      <c r="H5">
-        <v>0.4957264957264957</v>
-      </c>
-      <c r="I5">
-        <v>0.4159544159544159</v>
-      </c>
-      <c r="J5">
-        <v>0.383334832808517</v>
-      </c>
-      <c r="K5">
-        <v>10.2</v>
-      </c>
-      <c r="L5">
-        <v>0.2905982905982906</v>
-      </c>
-      <c r="M5">
-        <v>7.61</v>
-      </c>
-      <c r="N5">
-        <v>0.02917944785276074</v>
-      </c>
-      <c r="O5">
-        <v>0.7460784313725491</v>
-      </c>
-      <c r="P5">
-        <v>7.61</v>
-      </c>
-      <c r="Q5">
-        <v>0.02917944785276074</v>
-      </c>
-      <c r="R5">
-        <v>0.7460784313725491</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>108.2</v>
-      </c>
-      <c r="V5">
-        <v>0.4148773006134969</v>
-      </c>
-      <c r="W5">
-        <v>0.1033434650455927</v>
-      </c>
-      <c r="X5">
-        <v>0.04621177438595881</v>
-      </c>
-      <c r="Y5">
-        <v>0.05713169065963388</v>
-      </c>
-      <c r="Z5">
-        <v>-0.9915254237288138</v>
-      </c>
-      <c r="AA5">
-        <v>-0.3800862325304789</v>
-      </c>
-      <c r="AB5">
-        <v>0.04625573277293367</v>
-      </c>
-      <c r="AC5">
-        <v>-0.4263419653034125</v>
-      </c>
-      <c r="AD5">
-        <v>0.214</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>0.214</v>
-      </c>
-      <c r="AG5">
-        <v>-107.986</v>
-      </c>
-      <c r="AH5">
-        <v>0.0008198793934424973</v>
-      </c>
-      <c r="AI5">
-        <v>0.001847790422574128</v>
-      </c>
-      <c r="AJ5">
-        <v>-0.70664991427487</v>
-      </c>
-      <c r="AK5">
-        <v>-14.18255844496981</v>
-      </c>
-      <c r="AL5">
-        <v>0.017</v>
-      </c>
-      <c r="AM5">
-        <v>0.017</v>
-      </c>
-      <c r="AN5">
-        <v>0.01329192546583851</v>
-      </c>
-      <c r="AO5">
-        <v>858.8235294117646</v>
-      </c>
-      <c r="AP5">
-        <v>-6.707204968944099</v>
-      </c>
-      <c r="AQ5">
-        <v>858.8235294117646</v>
+        <v>-3.649965994105646</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_financial_svcs_non_bank_insurance.xlsx
@@ -587,41 +587,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.301</v>
+      </c>
+      <c r="E2">
+        <v>0.458</v>
+      </c>
       <c r="G2">
-        <v>0.4794635193133048</v>
+        <v>0.6057358490566037</v>
       </c>
       <c r="H2">
-        <v>0.4753218884120172</v>
+        <v>0.6037735849056604</v>
       </c>
       <c r="I2">
-        <v>0.3583690987124464</v>
+        <v>0.4915094339622641</v>
       </c>
       <c r="J2">
-        <v>0.2687768240343348</v>
+        <v>0.3270903512826464</v>
       </c>
       <c r="K2">
-        <v>5.34</v>
+        <v>68.39999999999999</v>
       </c>
       <c r="L2">
-        <v>0.0572961373390558</v>
+        <v>0.6452830188679245</v>
       </c>
       <c r="M2">
-        <v>19.28</v>
+        <v>21.18</v>
       </c>
       <c r="N2">
-        <v>0.0150390015600624</v>
+        <v>0.02164758789860997</v>
       </c>
       <c r="O2">
-        <v>3.610486891385768</v>
+        <v>0.3096491228070176</v>
       </c>
       <c r="P2">
-        <v>19.28</v>
+        <v>21.18</v>
       </c>
       <c r="Q2">
-        <v>0.0150390015600624</v>
+        <v>0.02164758789860997</v>
       </c>
       <c r="R2">
-        <v>3.610486891385768</v>
+        <v>0.3096491228070176</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -630,64 +636,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>593.5999999999999</v>
+        <v>595.9000000000001</v>
       </c>
       <c r="V2">
-        <v>0.4630265210608424</v>
+        <v>0.6090556009811938</v>
       </c>
       <c r="W2">
-        <v>0.0317270203152383</v>
+        <v>0.1272472251573268</v>
       </c>
       <c r="X2">
-        <v>0.08103441937928031</v>
+        <v>0.09225601246504447</v>
       </c>
       <c r="Y2">
-        <v>-0.04930739906404201</v>
+        <v>0.03499121269228231</v>
       </c>
       <c r="AB2">
-        <v>0.08137254261537472</v>
+        <v>0.09254755540617693</v>
       </c>
       <c r="AD2">
-        <v>5.28</v>
+        <v>4.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.28</v>
+        <v>4.3</v>
       </c>
       <c r="AG2">
-        <v>-588.3199999999999</v>
+        <v>-591.6000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.00410167174196756</v>
+        <v>0.004375699603134222</v>
       </c>
       <c r="AI2">
-        <v>0.01072560331518648</v>
+        <v>0.008019395747855278</v>
       </c>
       <c r="AJ2">
-        <v>-0.8481144043362933</v>
+        <v>-1.529472595656671</v>
       </c>
       <c r="AK2">
-        <v>5.806553493880777</v>
+        <v>9.909547738693444</v>
       </c>
       <c r="AL2">
-        <v>0.354</v>
+        <v>0.268</v>
       </c>
       <c r="AM2">
-        <v>-4.405</v>
+        <v>-18.02</v>
       </c>
       <c r="AN2">
-        <v>0.1423180592991914</v>
+        <v>0.07747747747747748</v>
       </c>
       <c r="AO2">
-        <v>94.35028248587572</v>
+        <v>194.4029850746268</v>
       </c>
       <c r="AP2">
-        <v>-15.85768194070081</v>
+        <v>-10.65945945945946</v>
       </c>
       <c r="AQ2">
-        <v>-7.582292849035188</v>
+        <v>-2.891231964483906</v>
       </c>
     </row>
     <row r="3">
@@ -707,40 +713,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.4953186274509804</v>
+        <v>0.6265270506108203</v>
       </c>
       <c r="H3">
-        <v>0.4950980392156863</v>
+        <v>0.6265270506108203</v>
       </c>
       <c r="I3">
-        <v>0.4240196078431373</v>
+        <v>0.4048865619546248</v>
       </c>
       <c r="J3">
-        <v>0.4240196078431373</v>
+        <v>0.2720208746335926</v>
       </c>
       <c r="K3">
-        <v>8.23</v>
+        <v>13.1</v>
       </c>
       <c r="L3">
-        <v>0.2017156862745098</v>
+        <v>0.2286212914485166</v>
       </c>
       <c r="M3">
-        <v>6.38</v>
+        <v>4.68</v>
       </c>
       <c r="N3">
-        <v>0.01846064814814815</v>
+        <v>0.02560175054704595</v>
       </c>
       <c r="O3">
-        <v>0.7752126366950182</v>
+        <v>0.3572519083969465</v>
       </c>
       <c r="P3">
-        <v>6.38</v>
+        <v>4.68</v>
       </c>
       <c r="Q3">
-        <v>0.01846064814814815</v>
+        <v>0.02560175054704595</v>
       </c>
       <c r="R3">
-        <v>0.7752126366950182</v>
+        <v>0.3572519083969465</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -749,64 +755,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>270.7</v>
+        <v>145.3</v>
       </c>
       <c r="V3">
-        <v>0.7832754629629629</v>
+        <v>0.7948577680525164</v>
       </c>
       <c r="W3">
-        <v>0.07309058614564833</v>
+        <v>0.09350463954318344</v>
       </c>
       <c r="X3">
-        <v>0.08124308890114179</v>
+        <v>0.09266158136483899</v>
       </c>
       <c r="Y3">
-        <v>-0.008152502755493465</v>
+        <v>0.000843058178344458</v>
       </c>
       <c r="AB3">
-        <v>0.08191933537333058</v>
+        <v>0.09324466724710391</v>
       </c>
       <c r="AD3">
-        <v>5.28</v>
+        <v>4.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5.28</v>
+        <v>4.3</v>
       </c>
       <c r="AG3">
-        <v>-265.42</v>
+        <v>-141</v>
       </c>
       <c r="AH3">
-        <v>0.01504787961696307</v>
+        <v>0.02298236237306253</v>
       </c>
       <c r="AI3">
-        <v>0.03551251008878128</v>
+        <v>0.0269254852849092</v>
       </c>
       <c r="AJ3">
-        <v>-3.310301820902968</v>
+        <v>-3.373205741626793</v>
       </c>
       <c r="AK3">
-        <v>2.175217177511883</v>
+        <v>-9.791666666666663</v>
       </c>
       <c r="AL3">
-        <v>0.095</v>
+        <v>0.268</v>
       </c>
       <c r="AM3">
-        <v>0.006000000000000005</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="AN3">
-        <v>0.2764397905759162</v>
+        <v>0.172</v>
       </c>
       <c r="AO3">
-        <v>182.1052631578947</v>
+        <v>86.56716417910447</v>
       </c>
       <c r="AP3">
-        <v>-13.89633507853403</v>
+        <v>-5.64</v>
       </c>
       <c r="AQ3">
-        <v>2883.333333333331</v>
+        <v>289.9999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -825,41 +831,47 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.301</v>
+      </c>
+      <c r="E4">
+        <v>0.458</v>
+      </c>
       <c r="G4">
-        <v>0.467118320610687</v>
+        <v>0.5812731006160163</v>
       </c>
       <c r="H4">
-        <v>0.4599236641221374</v>
+        <v>0.5770020533880903</v>
       </c>
       <c r="I4">
-        <v>0.3072519083969466</v>
+        <v>0.5934291581108829</v>
       </c>
       <c r="J4">
-        <v>0.1536259541984733</v>
+        <v>0.3911398384211183</v>
       </c>
       <c r="K4">
-        <v>-2.89</v>
+        <v>55.3</v>
       </c>
       <c r="L4">
-        <v>-0.0551526717557252</v>
+        <v>1.135523613963039</v>
       </c>
       <c r="M4">
-        <v>12.9</v>
+        <v>16.5</v>
       </c>
       <c r="N4">
-        <v>0.01377616403246476</v>
+        <v>0.02073906485671191</v>
       </c>
       <c r="O4">
-        <v>-4.463667820069204</v>
+        <v>0.298372513562387</v>
       </c>
       <c r="P4">
-        <v>12.9</v>
+        <v>16.5</v>
       </c>
       <c r="Q4">
-        <v>0.01377616403246476</v>
+        <v>0.02073906485671191</v>
       </c>
       <c r="R4">
-        <v>-4.463667820069204</v>
+        <v>0.298372513562387</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -868,22 +880,22 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>322.9</v>
+        <v>450.6</v>
       </c>
       <c r="V4">
-        <v>0.3448312686885946</v>
+        <v>0.5663650075414781</v>
       </c>
       <c r="W4">
-        <v>-0.009636545515171725</v>
+        <v>0.1609898107714701</v>
       </c>
       <c r="X4">
-        <v>0.08082574985741883</v>
+        <v>0.09185044356524996</v>
       </c>
       <c r="Y4">
-        <v>-0.09046229537259055</v>
+        <v>0.06913936720622019</v>
       </c>
       <c r="AB4">
-        <v>0.08082574985741883</v>
+        <v>0.09185044356524996</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -895,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-322.9</v>
+        <v>-450.6</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -904,28 +916,25 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.5263243683781581</v>
+        <v>-1.306086956521739</v>
       </c>
       <c r="AK4">
-        <v>-15.59903381642509</v>
+        <v>6.080971659919027</v>
       </c>
       <c r="AL4">
-        <v>0.259</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-4.411</v>
+        <v>-18.1</v>
       </c>
       <c r="AN4">
         <v>0</v>
       </c>
-      <c r="AO4">
-        <v>62.16216216216217</v>
-      </c>
       <c r="AP4">
-        <v>-17.93888888888889</v>
+        <v>-14.77377049180328</v>
       </c>
       <c r="AQ4">
-        <v>-3.649965994105646</v>
+        <v>-1.596685082872928</v>
       </c>
     </row>
   </sheetData>
